--- a/academias/Matemáticas - Estadisticos 20211.xlsx
+++ b/academias/Matemáticas - Estadisticos 20211.xlsx
@@ -711,13 +711,13 @@
         <v>22.73</v>
       </c>
       <c r="I5">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>22.73</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -746,13 +746,13 @@
         <v>12.9</v>
       </c>
       <c r="I6">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>12.9</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -769,25 +769,25 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>57.89</v>
+        <v>60.53</v>
       </c>
       <c r="H7">
-        <v>42.11</v>
+        <v>39.47</v>
       </c>
       <c r="I7">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>36.84</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -804,25 +804,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>68.56999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="H8">
-        <v>31.43</v>
+        <v>17.14</v>
       </c>
       <c r="I8">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>28.57</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -839,25 +839,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>63.64</v>
+        <v>69.7</v>
       </c>
       <c r="H9">
-        <v>36.36</v>
+        <v>30.3</v>
       </c>
       <c r="I9">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>27.27</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -886,13 +886,13 @@
         <v>13.89</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>13.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -909,25 +909,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>67.44</v>
+        <v>72.09</v>
       </c>
       <c r="H11">
-        <v>32.56</v>
+        <v>27.91</v>
       </c>
       <c r="I11">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="J11">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>32.56</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -944,25 +944,25 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="H12">
-        <v>16.28</v>
+        <v>11.63</v>
       </c>
       <c r="I12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -991,13 +991,13 @@
         <v>8.33</v>
       </c>
       <c r="I13">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1014,25 +1014,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>77.42</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H14">
-        <v>22.58</v>
+        <v>19.35</v>
       </c>
       <c r="I14">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>22.58</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1061,13 +1061,13 @@
         <v>42.86</v>
       </c>
       <c r="I15">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1096,13 +1096,13 @@
         <v>11.43</v>
       </c>
       <c r="I16">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>5.71</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1131,13 +1131,13 @@
         <v>33.33</v>
       </c>
       <c r="I17">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1154,25 +1154,25 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>71.05</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H18">
-        <v>28.95</v>
+        <v>26.32</v>
       </c>
       <c r="I18">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J18">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>28.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1201,13 +1201,13 @@
         <v>14.29</v>
       </c>
       <c r="I19">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1236,13 +1236,13 @@
         <v>26.92</v>
       </c>
       <c r="I20">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>26.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1259,25 +1259,25 @@
         <v>23</v>
       </c>
       <c r="E21">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>78.26000000000001</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H21">
-        <v>21.74</v>
+        <v>4.35</v>
       </c>
       <c r="I21">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>21.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1306,13 +1306,13 @@
         <v>34.38</v>
       </c>
       <c r="I22">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="J22">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>34.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1329,25 +1329,25 @@
         <v>34</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H23">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="I23">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>11.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1364,25 +1364,25 @@
         <v>36</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F24">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G24">
-        <v>33.33</v>
+        <v>58.33</v>
       </c>
       <c r="H24">
-        <v>66.67</v>
+        <v>41.67</v>
       </c>
       <c r="I24">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>66.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1399,25 +1399,25 @@
         <v>39</v>
       </c>
       <c r="E25">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>69.23</v>
+        <v>74.36</v>
       </c>
       <c r="H25">
-        <v>30.77</v>
+        <v>25.64</v>
       </c>
       <c r="I25">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="J25">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>30.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1434,25 +1434,25 @@
         <v>36</v>
       </c>
       <c r="E26">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F26">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G26">
-        <v>52.78</v>
+        <v>66.67</v>
       </c>
       <c r="H26">
-        <v>47.22</v>
+        <v>33.33</v>
       </c>
       <c r="I26">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="J26">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>47.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1469,25 +1469,25 @@
         <v>32</v>
       </c>
       <c r="E27">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>53.13</v>
+        <v>68.75</v>
       </c>
       <c r="H27">
-        <v>46.88</v>
+        <v>31.25</v>
       </c>
       <c r="I27">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="J27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>46.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1504,25 +1504,25 @@
         <v>43</v>
       </c>
       <c r="E28">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G28">
-        <v>67.44</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H28">
-        <v>32.56</v>
+        <v>20.93</v>
       </c>
       <c r="I28">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="J28">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>32.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1539,25 +1539,25 @@
         <v>29</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>68.97</v>
+        <v>79.31</v>
       </c>
       <c r="H29">
-        <v>31.03</v>
+        <v>20.69</v>
       </c>
       <c r="I29">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="J29">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>31.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1894,22 +1894,25 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>59.09</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>40.91</v>
+      </c>
+      <c r="I5">
+        <v>6.4</v>
       </c>
       <c r="J5">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1926,22 +1929,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>70.97</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>29.03</v>
+      </c>
+      <c r="I6">
+        <v>7.8</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1958,22 +1964,25 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>42.11</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>57.89</v>
+      </c>
+      <c r="I7">
+        <v>6.9</v>
       </c>
       <c r="J7">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1990,22 +1999,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>25.71</v>
+      </c>
+      <c r="I8">
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2022,22 +2034,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>54.55</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>45.45</v>
+      </c>
+      <c r="I9">
+        <v>7.4</v>
       </c>
       <c r="J9">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2054,22 +2069,25 @@
         <v>36</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I10">
+        <v>7.3</v>
       </c>
       <c r="J10">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2086,22 +2104,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>62.79</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>37.21</v>
+      </c>
+      <c r="I11">
+        <v>6.9</v>
       </c>
       <c r="J11">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>30.23</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2118,22 +2139,25 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>69.77</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>30.23</v>
+      </c>
+      <c r="I12">
+        <v>7.1</v>
       </c>
       <c r="J12">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>25.58</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2150,22 +2174,25 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>79.17</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>20.83</v>
+      </c>
+      <c r="I13">
+        <v>7.4</v>
       </c>
       <c r="J13">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2182,22 +2209,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>77.42</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>22.58</v>
+      </c>
+      <c r="I14">
+        <v>8.5</v>
       </c>
       <c r="J14">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2214,22 +2244,25 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>57.14</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>42.86</v>
+      </c>
+      <c r="I15">
+        <v>8.6</v>
       </c>
       <c r="J15">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2246,22 +2279,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F16">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>77.14</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>22.86</v>
+      </c>
+      <c r="I16">
+        <v>8.6</v>
       </c>
       <c r="J16">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2278,22 +2314,25 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F17">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>57.14</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>42.86</v>
+      </c>
+      <c r="I17">
+        <v>7.8</v>
       </c>
       <c r="J17">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2310,22 +2349,25 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>26.32</v>
+      </c>
+      <c r="I18">
+        <v>7.2</v>
       </c>
       <c r="J18">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2342,22 +2384,25 @@
         <v>35</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F19">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I19">
+        <v>7.9</v>
       </c>
       <c r="J19">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2374,22 +2419,25 @@
         <v>26</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F20">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>73.08</v>
       </c>
       <c r="H20">
-        <v>100</v>
+        <v>26.92</v>
+      </c>
+      <c r="I20">
+        <v>6.8</v>
       </c>
       <c r="J20">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2406,22 +2454,25 @@
         <v>23</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F21">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>4.35</v>
+      </c>
+      <c r="I21">
+        <v>7.5</v>
       </c>
       <c r="J21">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2438,22 +2489,25 @@
         <v>32</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>68.75</v>
       </c>
       <c r="H22">
-        <v>100</v>
+        <v>31.25</v>
+      </c>
+      <c r="I22">
+        <v>7.3</v>
       </c>
       <c r="J22">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2470,22 +2524,25 @@
         <v>34</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F23">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>97.06</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>2.94</v>
+      </c>
+      <c r="I23">
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2502,22 +2559,25 @@
         <v>36</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="H24">
-        <v>100</v>
+        <v>66.67</v>
+      </c>
+      <c r="I24">
+        <v>6.7</v>
       </c>
       <c r="J24">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>58.33</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2534,22 +2594,25 @@
         <v>39</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F25">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>58.97</v>
       </c>
       <c r="H25">
-        <v>100</v>
+        <v>41.03</v>
+      </c>
+      <c r="I25">
+        <v>6.8</v>
       </c>
       <c r="J25">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>41.03</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2566,22 +2629,25 @@
         <v>36</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F26">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>38.89</v>
       </c>
       <c r="H26">
-        <v>100</v>
+        <v>61.11</v>
+      </c>
+      <c r="I26">
+        <v>7.4</v>
       </c>
       <c r="J26">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2598,22 +2664,25 @@
         <v>32</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F27">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H27">
-        <v>100</v>
+        <v>34.38</v>
+      </c>
+      <c r="I27">
+        <v>6.7</v>
       </c>
       <c r="J27">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2630,22 +2699,25 @@
         <v>43</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F28">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>55.81</v>
       </c>
       <c r="H28">
-        <v>100</v>
+        <v>44.19</v>
+      </c>
+      <c r="I28">
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2662,22 +2734,25 @@
         <v>29</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F29">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>62.07</v>
       </c>
       <c r="H29">
-        <v>100</v>
+        <v>37.93</v>
+      </c>
+      <c r="I29">
+        <v>7.5</v>
       </c>
       <c r="J29">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>37.93</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3008,25 +3083,25 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>77.27</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H5">
-        <v>22.73</v>
+        <v>31.82</v>
       </c>
       <c r="I5">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>22.73</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3043,25 +3118,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>87.09999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="H6">
-        <v>12.9</v>
+        <v>16.13</v>
       </c>
       <c r="I6">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>12.9</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3078,25 +3153,25 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G7">
-        <v>57.89</v>
+        <v>50</v>
       </c>
       <c r="H7">
-        <v>42.11</v>
+        <v>50</v>
       </c>
       <c r="I7">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>36.84</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3113,25 +3188,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>68.56999999999999</v>
+        <v>77.14</v>
       </c>
       <c r="H8">
-        <v>31.43</v>
+        <v>22.86</v>
       </c>
       <c r="I8">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>28.57</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3160,13 +3235,13 @@
         <v>36.36</v>
       </c>
       <c r="I9">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>27.27</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3198,10 +3273,10 @@
         <v>7</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>13.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3218,25 +3293,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>67.44</v>
+        <v>72.09</v>
       </c>
       <c r="H11">
-        <v>32.56</v>
+        <v>27.91</v>
       </c>
       <c r="I11">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J11">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>32.56</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3253,25 +3328,25 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="H12">
-        <v>16.28</v>
+        <v>11.63</v>
       </c>
       <c r="I12">
         <v>6.8</v>
       </c>
       <c r="J12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3300,13 +3375,13 @@
         <v>8.33</v>
       </c>
       <c r="I13">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3323,25 +3398,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>77.42</v>
+        <v>83.87</v>
       </c>
       <c r="H14">
-        <v>22.58</v>
+        <v>16.13</v>
       </c>
       <c r="I14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>22.58</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3358,25 +3433,25 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G15">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H15">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
       <c r="I15">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3393,25 +3468,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H16">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
       <c r="I16">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>5.71</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3428,25 +3503,25 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>66.67</v>
+        <v>76.19</v>
       </c>
       <c r="H17">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
       <c r="I17">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3463,25 +3538,25 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>71.05</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H18">
-        <v>28.95</v>
+        <v>26.32</v>
       </c>
       <c r="I18">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J18">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>28.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3513,10 +3588,10 @@
         <v>7.8</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3545,13 +3620,13 @@
         <v>26.92</v>
       </c>
       <c r="I20">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="J20">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>26.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3568,25 +3643,25 @@
         <v>23</v>
       </c>
       <c r="E21">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>78.26000000000001</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H21">
-        <v>21.74</v>
+        <v>4.35</v>
       </c>
       <c r="I21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>21.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3603,25 +3678,25 @@
         <v>32</v>
       </c>
       <c r="E22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>65.63</v>
+        <v>68.75</v>
       </c>
       <c r="H22">
-        <v>34.38</v>
+        <v>31.25</v>
       </c>
       <c r="I22">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="J22">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>34.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3638,25 +3713,25 @@
         <v>34</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>88.23999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="H23">
-        <v>11.76</v>
+        <v>2.94</v>
       </c>
       <c r="I23">
         <v>8</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>11.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3673,25 +3748,25 @@
         <v>36</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F24">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G24">
-        <v>33.33</v>
+        <v>58.33</v>
       </c>
       <c r="H24">
-        <v>66.67</v>
+        <v>41.67</v>
       </c>
       <c r="I24">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>66.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3708,25 +3783,25 @@
         <v>39</v>
       </c>
       <c r="E25">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>69.23</v>
+        <v>74.36</v>
       </c>
       <c r="H25">
-        <v>30.77</v>
+        <v>25.64</v>
       </c>
       <c r="I25">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J25">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>30.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -3743,25 +3818,25 @@
         <v>36</v>
       </c>
       <c r="E26">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F26">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G26">
-        <v>52.78</v>
+        <v>66.67</v>
       </c>
       <c r="H26">
-        <v>47.22</v>
+        <v>33.33</v>
       </c>
       <c r="I26">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="J26">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>47.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3778,25 +3853,25 @@
         <v>32</v>
       </c>
       <c r="E27">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>53.13</v>
+        <v>68.75</v>
       </c>
       <c r="H27">
-        <v>46.88</v>
+        <v>31.25</v>
       </c>
       <c r="I27">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="J27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>46.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3813,25 +3888,25 @@
         <v>43</v>
       </c>
       <c r="E28">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G28">
-        <v>67.44</v>
+        <v>83.72</v>
       </c>
       <c r="H28">
-        <v>32.56</v>
+        <v>16.28</v>
       </c>
       <c r="I28">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J28">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>32.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3848,25 +3923,25 @@
         <v>29</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>68.97</v>
+        <v>79.31</v>
       </c>
       <c r="H29">
-        <v>31.03</v>
+        <v>20.69</v>
       </c>
       <c r="I29">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J29">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>31.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20211.xlsx
+++ b/academias/Matemáticas - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -187,6 +187,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -239,8 +243,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -541,42 +547,45 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -599,19 +608,19 @@
       <c r="F2">
         <v>17</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>57.5</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>42.5</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J2">
         <v>17</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>42.5</v>
       </c>
     </row>
@@ -634,19 +643,19 @@
       <c r="F3">
         <v>14</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>68.18000000000001</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>31.82</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>9.5</v>
       </c>
       <c r="J3">
         <v>14</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>31.82</v>
       </c>
     </row>
@@ -669,19 +678,19 @@
       <c r="F4">
         <v>7</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>66.67</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>33.33</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>9.9</v>
       </c>
       <c r="J4">
         <v>7</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>33.33</v>
       </c>
     </row>
@@ -704,19 +713,19 @@
       <c r="F5">
         <v>5</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>77.27</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>22.73</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>6.7</v>
       </c>
       <c r="J5">
         <v>3</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>13.64</v>
       </c>
     </row>
@@ -739,19 +748,19 @@
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>87.09999999999999</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>12.9</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>8.4</v>
       </c>
       <c r="J6">
         <v>3</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>9.68</v>
       </c>
     </row>
@@ -774,19 +783,19 @@
       <c r="F7">
         <v>15</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>60.53</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>39.47</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.8</v>
       </c>
       <c r="J7">
         <v>9</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>23.68</v>
       </c>
     </row>
@@ -809,19 +818,19 @@
       <c r="F8">
         <v>6</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>82.86</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>17.14</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.6</v>
       </c>
       <c r="J8">
         <v>3</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>8.57</v>
       </c>
     </row>
@@ -844,19 +853,19 @@
       <c r="F9">
         <v>10</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>69.7</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>30.3</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.7</v>
       </c>
       <c r="J9">
         <v>7</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>21.21</v>
       </c>
     </row>
@@ -879,19 +888,19 @@
       <c r="F10">
         <v>5</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>86.11</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>13.89</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>6.7</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -914,19 +923,19 @@
       <c r="F11">
         <v>12</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>72.09</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>27.91</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>6.3</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>2.33</v>
       </c>
     </row>
@@ -949,19 +958,19 @@
       <c r="F12">
         <v>5</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>88.37</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>11.63</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>6.6</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -984,19 +993,19 @@
       <c r="F13">
         <v>2</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>91.67</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>8.33</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>6.5</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1019,19 +1028,19 @@
       <c r="F14">
         <v>6</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>80.65000000000001</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>19.35</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>7.8</v>
       </c>
       <c r="J14">
         <v>5</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>16.13</v>
       </c>
     </row>
@@ -1054,19 +1063,19 @@
       <c r="F15">
         <v>9</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>57.14</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>42.86</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>7.6</v>
       </c>
       <c r="J15">
         <v>7</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>33.33</v>
       </c>
     </row>
@@ -1089,19 +1098,19 @@
       <c r="F16">
         <v>4</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>88.56999999999999</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>11.43</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>2.86</v>
       </c>
     </row>
@@ -1124,19 +1133,19 @@
       <c r="F17">
         <v>7</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>66.67</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>33.33</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>7.4</v>
       </c>
       <c r="J17">
         <v>5</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>23.81</v>
       </c>
     </row>
@@ -1159,19 +1168,19 @@
       <c r="F18">
         <v>10</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>73.68000000000001</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>26.32</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>6.7</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1194,19 +1203,19 @@
       <c r="F19">
         <v>5</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>85.70999999999999</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>14.29</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>7.4</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1229,19 +1238,19 @@
       <c r="F20">
         <v>7</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>73.08</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>26.92</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>6.3</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1264,19 +1273,19 @@
       <c r="F21">
         <v>1</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>95.65000000000001</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>4.35</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>7.1</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1299,19 +1308,19 @@
       <c r="F22">
         <v>11</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>65.63</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>34.38</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>6.7</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1334,19 +1343,19 @@
       <c r="F23">
         <v>2</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>94.12</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>5.88</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>7.8</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1369,19 +1378,19 @@
       <c r="F24">
         <v>15</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>58.33</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>41.67</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="2">
         <v>6</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1404,19 +1413,19 @@
       <c r="F25">
         <v>10</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>74.36</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>25.64</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="2">
         <v>6.9</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1439,19 +1448,19 @@
       <c r="F26">
         <v>12</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>66.67</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>33.33</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="2">
         <v>6.6</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1474,19 +1483,19 @@
       <c r="F27">
         <v>10</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>68.75</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>31.25</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>6.3</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1509,19 +1518,19 @@
       <c r="F28">
         <v>9</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>79.06999999999999</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>20.93</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="2">
         <v>6.7</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1544,19 +1553,19 @@
       <c r="F29">
         <v>6</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>79.31</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>20.69</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="2">
         <v>7</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1579,19 +1588,19 @@
       <c r="F30">
         <v>10</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>70.59</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>29.41</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="2">
         <v>7.6</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1614,19 +1623,19 @@
       <c r="F31">
         <v>10</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>67.73999999999999</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>32.26</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="2">
         <v>7.3</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1649,19 +1658,19 @@
       <c r="F32">
         <v>7</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>72</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>28</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="2">
         <v>7</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>4</v>
       </c>
     </row>
@@ -1684,19 +1693,19 @@
       <c r="F33">
         <v>11</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="1">
         <v>68.56999999999999</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>31.43</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="2">
         <v>7.1</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="1">
         <v>2.86</v>
       </c>
     </row>
@@ -1719,19 +1728,19 @@
       <c r="F34">
         <v>12</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>63.64</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>36.36</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="2">
         <v>6.6</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1745,42 +1754,45 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1803,16 +1815,16 @@
       <c r="F2">
         <v>40</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
         <v>100</v>
       </c>
       <c r="J2">
         <v>40</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1835,16 +1847,16 @@
       <c r="F3">
         <v>44</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
         <v>100</v>
       </c>
       <c r="J3">
         <v>44</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1867,16 +1879,16 @@
       <c r="F4">
         <v>21</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
         <v>100</v>
       </c>
       <c r="J4">
         <v>21</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1899,19 +1911,19 @@
       <c r="F5">
         <v>9</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>59.09</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>40.91</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>6.4</v>
       </c>
       <c r="J5">
         <v>5</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>22.73</v>
       </c>
     </row>
@@ -1934,19 +1946,19 @@
       <c r="F6">
         <v>9</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>70.97</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>29.03</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7.8</v>
       </c>
       <c r="J6">
         <v>7</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>22.58</v>
       </c>
     </row>
@@ -1969,19 +1981,19 @@
       <c r="F7">
         <v>22</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>42.11</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>57.89</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>6.9</v>
       </c>
       <c r="J7">
         <v>13</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>34.21</v>
       </c>
     </row>
@@ -2004,19 +2016,19 @@
       <c r="F8">
         <v>9</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>74.29000000000001</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>25.71</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.8</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>11.43</v>
       </c>
     </row>
@@ -2039,19 +2051,19 @@
       <c r="F9">
         <v>15</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>54.55</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>45.45</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.4</v>
       </c>
       <c r="J9">
         <v>12</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>36.36</v>
       </c>
     </row>
@@ -2074,19 +2086,19 @@
       <c r="F10">
         <v>9</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>75</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>25</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.3</v>
       </c>
       <c r="J10">
         <v>7</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>19.44</v>
       </c>
     </row>
@@ -2109,19 +2121,19 @@
       <c r="F11">
         <v>16</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>62.79</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>37.21</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>6.9</v>
       </c>
       <c r="J11">
         <v>13</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>30.23</v>
       </c>
     </row>
@@ -2144,19 +2156,19 @@
       <c r="F12">
         <v>13</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>69.77</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>30.23</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>7.1</v>
       </c>
       <c r="J12">
         <v>11</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>25.58</v>
       </c>
     </row>
@@ -2179,19 +2191,19 @@
       <c r="F13">
         <v>5</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>79.17</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>20.83</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>7.4</v>
       </c>
       <c r="J13">
         <v>5</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>20.83</v>
       </c>
     </row>
@@ -2214,19 +2226,19 @@
       <c r="F14">
         <v>7</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>77.42</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>22.58</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>8.5</v>
       </c>
       <c r="J14">
         <v>7</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>22.58</v>
       </c>
     </row>
@@ -2249,19 +2261,19 @@
       <c r="F15">
         <v>9</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>57.14</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>42.86</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>8.6</v>
       </c>
       <c r="J15">
         <v>9</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>42.86</v>
       </c>
     </row>
@@ -2284,19 +2296,19 @@
       <c r="F16">
         <v>8</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>77.14</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>22.86</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>8.6</v>
       </c>
       <c r="J16">
         <v>8</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>22.86</v>
       </c>
     </row>
@@ -2319,19 +2331,19 @@
       <c r="F17">
         <v>9</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>57.14</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>42.86</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>7.8</v>
       </c>
       <c r="J17">
         <v>9</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>42.86</v>
       </c>
     </row>
@@ -2354,19 +2366,19 @@
       <c r="F18">
         <v>10</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>73.68000000000001</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>26.32</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>7.2</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2389,19 +2401,19 @@
       <c r="F19">
         <v>5</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>85.70999999999999</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>14.29</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>7.9</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2424,19 +2436,19 @@
       <c r="F20">
         <v>7</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>73.08</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>26.92</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>6.8</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2459,19 +2471,19 @@
       <c r="F21">
         <v>1</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>95.65000000000001</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>4.35</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>7.5</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2494,19 +2506,19 @@
       <c r="F22">
         <v>10</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>68.75</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>31.25</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>7.3</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2529,19 +2541,19 @@
       <c r="F23">
         <v>1</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>97.06</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>2.94</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>8</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2564,19 +2576,19 @@
       <c r="F24">
         <v>24</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>33.33</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>66.67</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="2">
         <v>6.7</v>
       </c>
       <c r="J24">
         <v>21</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>58.33</v>
       </c>
     </row>
@@ -2599,19 +2611,19 @@
       <c r="F25">
         <v>16</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>58.97</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>41.03</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="2">
         <v>6.8</v>
       </c>
       <c r="J25">
         <v>16</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>41.03</v>
       </c>
     </row>
@@ -2634,19 +2646,19 @@
       <c r="F26">
         <v>22</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>38.89</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>61.11</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="2">
         <v>7.4</v>
       </c>
       <c r="J26">
         <v>22</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>61.11</v>
       </c>
     </row>
@@ -2669,19 +2681,19 @@
       <c r="F27">
         <v>11</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>65.63</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>34.38</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>6.7</v>
       </c>
       <c r="J27">
         <v>9</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>28.13</v>
       </c>
     </row>
@@ -2704,19 +2716,19 @@
       <c r="F28">
         <v>19</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>55.81</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>44.19</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="2">
         <v>7</v>
       </c>
       <c r="J28">
         <v>19</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>44.19</v>
       </c>
     </row>
@@ -2739,19 +2751,19 @@
       <c r="F29">
         <v>11</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>62.07</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>37.93</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="2">
         <v>7.5</v>
       </c>
       <c r="J29">
         <v>11</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>37.93</v>
       </c>
     </row>
@@ -2774,16 +2786,16 @@
       <c r="F30">
         <v>34</v>
       </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
         <v>100</v>
       </c>
       <c r="J30">
         <v>34</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2806,16 +2818,16 @@
       <c r="F31">
         <v>31</v>
       </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
         <v>100</v>
       </c>
       <c r="J31">
         <v>31</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2838,16 +2850,16 @@
       <c r="F32">
         <v>25</v>
       </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
         <v>100</v>
       </c>
       <c r="J32">
         <v>25</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2870,16 +2882,16 @@
       <c r="F33">
         <v>35</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
         <v>100</v>
       </c>
       <c r="J33">
         <v>35</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2902,16 +2914,16 @@
       <c r="F34">
         <v>33</v>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
         <v>100</v>
       </c>
       <c r="J34">
         <v>33</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2925,42 +2937,45 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2983,19 +2998,19 @@
       <c r="F2">
         <v>17</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>57.5</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>42.5</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J2">
         <v>17</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>42.5</v>
       </c>
     </row>
@@ -3018,19 +3033,19 @@
       <c r="F3">
         <v>14</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>68.18000000000001</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>31.82</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>9.5</v>
       </c>
       <c r="J3">
         <v>14</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>31.82</v>
       </c>
     </row>
@@ -3053,19 +3068,19 @@
       <c r="F4">
         <v>7</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>66.67</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>33.33</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>9.9</v>
       </c>
       <c r="J4">
         <v>7</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>33.33</v>
       </c>
     </row>
@@ -3088,19 +3103,19 @@
       <c r="F5">
         <v>7</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>68.18000000000001</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>31.82</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>6.7</v>
       </c>
       <c r="J5">
         <v>3</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>13.64</v>
       </c>
     </row>
@@ -3123,19 +3138,19 @@
       <c r="F6">
         <v>5</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>83.87</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>16.13</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J6">
         <v>3</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>9.68</v>
       </c>
     </row>
@@ -3158,19 +3173,19 @@
       <c r="F7">
         <v>19</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>50</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>50</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.6</v>
       </c>
       <c r="J7">
         <v>9</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>23.68</v>
       </c>
     </row>
@@ -3193,19 +3208,19 @@
       <c r="F8">
         <v>8</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>77.14</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>22.86</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.8</v>
       </c>
       <c r="J8">
         <v>3</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>8.57</v>
       </c>
     </row>
@@ -3228,19 +3243,19 @@
       <c r="F9">
         <v>12</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>63.64</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>36.36</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.6</v>
       </c>
       <c r="J9">
         <v>7</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>21.21</v>
       </c>
     </row>
@@ -3263,19 +3278,19 @@
       <c r="F10">
         <v>5</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>86.11</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>13.89</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3298,19 +3313,19 @@
       <c r="F11">
         <v>12</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>72.09</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>27.91</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>6.4</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>2.33</v>
       </c>
     </row>
@@ -3333,19 +3348,19 @@
       <c r="F12">
         <v>5</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>88.37</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>11.63</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>6.8</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3368,19 +3383,19 @@
       <c r="F13">
         <v>2</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>91.67</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>8.33</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>7</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3403,19 +3418,19 @@
       <c r="F14">
         <v>5</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>83.87</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>16.13</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J14">
         <v>5</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>16.13</v>
       </c>
     </row>
@@ -3438,19 +3453,19 @@
       <c r="F15">
         <v>7</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>66.67</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>33.33</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>8.1</v>
       </c>
       <c r="J15">
         <v>7</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>33.33</v>
       </c>
     </row>
@@ -3473,19 +3488,19 @@
       <c r="F16">
         <v>3</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>91.43000000000001</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>8.57</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>8.5</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>2.86</v>
       </c>
     </row>
@@ -3508,19 +3523,19 @@
       <c r="F17">
         <v>5</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>76.19</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>23.81</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>7.7</v>
       </c>
       <c r="J17">
         <v>5</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>23.81</v>
       </c>
     </row>
@@ -3543,19 +3558,19 @@
       <c r="F18">
         <v>10</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>73.68000000000001</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>26.32</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>7.1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3578,19 +3593,19 @@
       <c r="F19">
         <v>5</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>85.70999999999999</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>14.29</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>7.8</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3613,19 +3628,19 @@
       <c r="F20">
         <v>7</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>73.08</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>26.92</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>6.5</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3648,19 +3663,19 @@
       <c r="F21">
         <v>1</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>95.65000000000001</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>4.35</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>7.6</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3683,19 +3698,19 @@
       <c r="F22">
         <v>10</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>68.75</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>31.25</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>6.9</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3718,19 +3733,19 @@
       <c r="F23">
         <v>1</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>97.06</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>2.94</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>8</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3753,19 +3768,19 @@
       <c r="F24">
         <v>15</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>58.33</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>41.67</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="2">
         <v>6</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3788,19 +3803,19 @@
       <c r="F25">
         <v>10</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>74.36</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>25.64</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="2">
         <v>6.8</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3823,19 +3838,19 @@
       <c r="F26">
         <v>12</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>66.67</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>33.33</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="2">
         <v>6.6</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3858,19 +3873,19 @@
       <c r="F27">
         <v>10</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>68.75</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>31.25</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>6.4</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3893,19 +3908,19 @@
       <c r="F28">
         <v>7</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>83.72</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>16.28</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="2">
         <v>6.8</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3928,19 +3943,19 @@
       <c r="F29">
         <v>6</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>79.31</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>20.69</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="2">
         <v>7.1</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3963,19 +3978,19 @@
       <c r="F30">
         <v>10</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>70.59</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>29.41</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="2">
         <v>7.6</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3998,19 +4013,19 @@
       <c r="F31">
         <v>10</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>67.73999999999999</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>32.26</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="2">
         <v>7.3</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4033,19 +4048,19 @@
       <c r="F32">
         <v>7</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>72</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>28</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="2">
         <v>7</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>4</v>
       </c>
     </row>
@@ -4068,19 +4083,19 @@
       <c r="F33">
         <v>11</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="1">
         <v>68.56999999999999</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>31.43</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="2">
         <v>7.1</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="1">
         <v>2.86</v>
       </c>
     </row>
@@ -4103,19 +4118,19 @@
       <c r="F34">
         <v>12</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>63.64</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>36.36</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="2">
         <v>6.6</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Matemáticas - Estadisticos 20211.xlsx
+++ b/academias/Matemáticas - Estadisticos 20211.xlsx
@@ -188,7 +188,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Matemáticas - Estadisticos 20211.xlsx
+++ b/academias/Matemáticas - Estadisticos 20211.xlsx
@@ -603,25 +603,25 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1">
-        <v>57.5</v>
+        <v>65</v>
       </c>
       <c r="H2" s="1">
-        <v>42.5</v>
+        <v>35</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K2" s="1">
-        <v>42.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -638,25 +638,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>68.18000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="H3" s="1">
-        <v>31.82</v>
+        <v>22.73</v>
       </c>
       <c r="I3" s="2">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K3" s="1">
-        <v>31.82</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -673,25 +673,25 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>66.67</v>
+        <v>76.19</v>
       </c>
       <c r="H4" s="1">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
       <c r="I4" s="2">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K4" s="1">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1093,25 +1093,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>11.43</v>
+        <v>8.57</v>
       </c>
       <c r="I16" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1653,25 +1653,25 @@
         <v>25</v>
       </c>
       <c r="E32">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G32" s="1">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H32" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I32" s="2">
         <v>7</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1688,25 +1688,25 @@
         <v>35</v>
       </c>
       <c r="E33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F33">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>68.56999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H33" s="1">
-        <v>31.43</v>
+        <v>28.57</v>
       </c>
       <c r="I33" s="2">
         <v>7.1</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1810,22 +1810,25 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>62.5</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.1</v>
       </c>
       <c r="J2">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1842,22 +1845,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>56.82</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>43.18</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>43.18</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1874,22 +1880,25 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>57.14</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>42.86</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.9</v>
       </c>
       <c r="J4">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2256,25 +2265,25 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H15" s="1">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
       <c r="I15" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K15" s="1">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2291,25 +2300,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>77.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>22.86</v>
+        <v>14.29</v>
       </c>
       <c r="I16" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K16" s="1">
-        <v>22.86</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2326,25 +2335,25 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" s="1">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H17" s="1">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
       <c r="I17" s="2">
         <v>7.8</v>
       </c>
       <c r="J17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K17" s="1">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2781,22 +2790,25 @@
         <v>34</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F30">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>17.65</v>
+      </c>
+      <c r="I30" s="2">
+        <v>7.6</v>
       </c>
       <c r="J30">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2813,22 +2825,25 @@
         <v>31</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F31">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>74.19</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>25.81</v>
+      </c>
+      <c r="I31" s="2">
+        <v>7.8</v>
       </c>
       <c r="J31">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2845,22 +2860,25 @@
         <v>25</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F32">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>36</v>
+      </c>
+      <c r="I32" s="2">
+        <v>7.2</v>
       </c>
       <c r="J32">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2877,22 +2895,25 @@
         <v>35</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F33">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>28.57</v>
+      </c>
+      <c r="I33" s="2">
+        <v>7.2</v>
       </c>
       <c r="J33">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2909,22 +2930,25 @@
         <v>33</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F34">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>57.58</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>42.42</v>
+      </c>
+      <c r="I34" s="2">
+        <v>6.6</v>
       </c>
       <c r="J34">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2993,25 +3017,25 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1">
-        <v>57.5</v>
+        <v>65</v>
       </c>
       <c r="H2" s="1">
-        <v>42.5</v>
+        <v>35</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K2" s="1">
-        <v>42.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3028,25 +3052,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>68.18000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="H3" s="1">
-        <v>31.82</v>
+        <v>22.73</v>
       </c>
       <c r="I3" s="2">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K3" s="1">
-        <v>31.82</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3063,25 +3087,25 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>66.67</v>
+        <v>76.19</v>
       </c>
       <c r="H4" s="1">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
       <c r="I4" s="2">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K4" s="1">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3460,7 +3484,7 @@
         <v>33.33</v>
       </c>
       <c r="I15" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -3483,25 +3507,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
       <c r="I16" s="2">
         <v>8.5</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3530,7 +3554,7 @@
         <v>23.81</v>
       </c>
       <c r="I17" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
         <v>5</v>
@@ -3973,19 +3997,19 @@
         <v>34</v>
       </c>
       <c r="E30">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G30" s="1">
-        <v>70.59</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>29.41</v>
+        <v>17.65</v>
       </c>
       <c r="I30" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4008,19 +4032,19 @@
         <v>31</v>
       </c>
       <c r="E31">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G31" s="1">
-        <v>67.73999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="H31" s="1">
-        <v>32.26</v>
+        <v>25.81</v>
       </c>
       <c r="I31" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4043,25 +4067,25 @@
         <v>25</v>
       </c>
       <c r="E32">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G32" s="1">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H32" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I32" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4078,25 +4102,25 @@
         <v>35</v>
       </c>
       <c r="E33">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F33">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>68.56999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H33" s="1">
-        <v>31.43</v>
+        <v>28.57</v>
       </c>
       <c r="I33" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4113,19 +4137,19 @@
         <v>33</v>
       </c>
       <c r="E34">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F34">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G34" s="1">
-        <v>63.64</v>
+        <v>57.58</v>
       </c>
       <c r="H34" s="1">
-        <v>36.36</v>
+        <v>42.42</v>
       </c>
       <c r="I34" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J34">
         <v>0</v>

--- a/academias/Matemáticas - Estadisticos 20211.xlsx
+++ b/academias/Matemáticas - Estadisticos 20211.xlsx
@@ -1023,25 +1023,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>80.65000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="H14" s="1">
-        <v>19.35</v>
+        <v>16.13</v>
       </c>
       <c r="I14" s="2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1070,13 +1070,13 @@
         <v>42.86</v>
       </c>
       <c r="I15" s="2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="J15">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1128,25 +1128,25 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F17">
+        <v>6</v>
+      </c>
+      <c r="G17" s="1">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H17" s="1">
+        <v>28.57</v>
+      </c>
+      <c r="I17" s="2">
         <v>7</v>
       </c>
-      <c r="G17" s="1">
-        <v>66.67</v>
-      </c>
-      <c r="H17" s="1">
-        <v>33.33</v>
-      </c>
-      <c r="I17" s="2">
-        <v>7.4</v>
-      </c>
       <c r="J17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>23.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2230,25 +2230,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>77.42</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>22.58</v>
+        <v>19.35</v>
       </c>
       <c r="I14" s="2">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="J14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>22.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2265,25 +2265,25 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1">
-        <v>61.9</v>
+        <v>66.67</v>
       </c>
       <c r="H15" s="1">
-        <v>38.1</v>
+        <v>33.33</v>
       </c>
       <c r="I15" s="2">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>38.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2300,25 +2300,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>85.70999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>14.29</v>
+        <v>5.71</v>
       </c>
       <c r="I16" s="2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2335,25 +2335,25 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>61.9</v>
+        <v>80.95</v>
       </c>
       <c r="H17" s="1">
-        <v>38.1</v>
+        <v>19.05</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J17">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>38.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2615,25 +2615,25 @@
         <v>39</v>
       </c>
       <c r="E25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" s="1">
-        <v>58.97</v>
+        <v>61.54</v>
       </c>
       <c r="H25" s="1">
-        <v>41.03</v>
+        <v>38.46</v>
       </c>
       <c r="I25" s="2">
         <v>6.8</v>
       </c>
       <c r="J25">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K25" s="1">
-        <v>41.03</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2650,25 +2650,25 @@
         <v>36</v>
       </c>
       <c r="E26">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F26">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G26" s="1">
-        <v>38.89</v>
+        <v>44.44</v>
       </c>
       <c r="H26" s="1">
-        <v>61.11</v>
+        <v>55.56</v>
       </c>
       <c r="I26" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J26">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K26" s="1">
-        <v>61.11</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3437,25 +3437,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>83.87</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>16.13</v>
+        <v>19.35</v>
       </c>
       <c r="I14" s="2">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3484,13 +3484,13 @@
         <v>33.33</v>
       </c>
       <c r="I15" s="2">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3519,7 +3519,7 @@
         <v>5.71</v>
       </c>
       <c r="I16" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3542,25 +3542,25 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H17" s="1">
-        <v>23.81</v>
+        <v>19.05</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>23.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20211.xlsx
+++ b/academias/Matemáticas - Estadisticos 20211.xlsx
@@ -778,25 +778,25 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>60.53</v>
+        <v>63.16</v>
       </c>
       <c r="H7" s="1">
-        <v>39.47</v>
+        <v>36.84</v>
       </c>
       <c r="I7" s="2">
         <v>7.8</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K7" s="1">
-        <v>23.68</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1985,25 +1985,25 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G7" s="1">
-        <v>42.11</v>
+        <v>44.74</v>
       </c>
       <c r="H7" s="1">
-        <v>57.89</v>
+        <v>55.26</v>
       </c>
       <c r="I7" s="2">
         <v>6.9</v>
       </c>
       <c r="J7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K7" s="1">
-        <v>34.21</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3192,25 +3192,25 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="H7" s="1">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="I7" s="2">
         <v>7.6</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K7" s="1">
-        <v>23.68</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="8" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20211.xlsx
+++ b/academias/Matemáticas - Estadisticos 20211.xlsx
@@ -603,25 +603,25 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -638,25 +638,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -673,25 +673,25 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>76.19</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>23.81</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>23.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -708,25 +708,25 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>77.27</v>
+        <v>90.91</v>
       </c>
       <c r="H5" s="1">
-        <v>22.73</v>
+        <v>9.09</v>
       </c>
       <c r="I5" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -743,25 +743,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>87.09999999999999</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>12.9</v>
+        <v>9.68</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -790,13 +790,13 @@
         <v>36.84</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -825,13 +825,13 @@
         <v>17.14</v>
       </c>
       <c r="I8" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -848,25 +848,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="H9" s="1">
-        <v>30.3</v>
+        <v>27.27</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>21.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -933,10 +933,10 @@
         <v>6.3</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1615,19 +1615,19 @@
         <v>52</v>
       </c>
       <c r="D31">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31">
         <v>21</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G31" s="1">
-        <v>67.73999999999999</v>
+        <v>65.63</v>
       </c>
       <c r="H31" s="1">
-        <v>32.26</v>
+        <v>34.38</v>
       </c>
       <c r="I31" s="2">
         <v>7.3</v>
@@ -1810,25 +1810,25 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>62.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1845,25 +1845,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>56.82</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>43.18</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="J3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>43.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1880,25 +1880,25 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>57.14</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>42.86</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>42.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1915,25 +1915,25 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>59.09</v>
+        <v>72.73</v>
       </c>
       <c r="H5" s="1">
-        <v>40.91</v>
+        <v>27.27</v>
       </c>
       <c r="I5" s="2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1950,25 +1950,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>70.97</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>29.03</v>
+        <v>9.68</v>
       </c>
       <c r="I6" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>22.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1985,25 +1985,25 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1">
-        <v>44.74</v>
+        <v>52.63</v>
       </c>
       <c r="H7" s="1">
-        <v>55.26</v>
+        <v>47.37</v>
       </c>
       <c r="I7" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>31.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2032,13 +2032,13 @@
         <v>25.71</v>
       </c>
       <c r="I8" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>11.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2055,25 +2055,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9" s="1">
-        <v>54.55</v>
+        <v>63.64</v>
       </c>
       <c r="H9" s="1">
-        <v>45.45</v>
+        <v>36.36</v>
       </c>
       <c r="I9" s="2">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>36.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2090,25 +2090,25 @@
         <v>36</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="H10" s="1">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J10">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>19.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2125,25 +2125,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G11" s="1">
-        <v>62.79</v>
+        <v>69.77</v>
       </c>
       <c r="H11" s="1">
-        <v>37.21</v>
+        <v>30.23</v>
       </c>
       <c r="I11" s="2">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="J11">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>30.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2160,25 +2160,25 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>69.77</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>30.23</v>
+        <v>20.93</v>
       </c>
       <c r="I12" s="2">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>25.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2195,25 +2195,25 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>79.17</v>
+        <v>87.5</v>
       </c>
       <c r="H13" s="1">
-        <v>20.83</v>
+        <v>12.5</v>
       </c>
       <c r="I13" s="2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>20.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2580,25 +2580,25 @@
         <v>36</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F24">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G24" s="1">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="H24" s="1">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="I24" s="2">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="J24">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>58.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2615,25 +2615,25 @@
         <v>39</v>
       </c>
       <c r="E25">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G25" s="1">
-        <v>61.54</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>38.46</v>
+        <v>28.21</v>
       </c>
       <c r="I25" s="2">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="J25">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>38.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2650,25 +2650,25 @@
         <v>36</v>
       </c>
       <c r="E26">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F26">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G26" s="1">
-        <v>44.44</v>
+        <v>58.33</v>
       </c>
       <c r="H26" s="1">
-        <v>55.56</v>
+        <v>41.67</v>
       </c>
       <c r="I26" s="2">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="J26">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>52.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2685,25 +2685,25 @@
         <v>32</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G27" s="1">
-        <v>65.63</v>
+        <v>68.75</v>
       </c>
       <c r="H27" s="1">
-        <v>34.38</v>
+        <v>31.25</v>
       </c>
       <c r="I27" s="2">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="J27">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>28.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2720,25 +2720,25 @@
         <v>43</v>
       </c>
       <c r="E28">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F28">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G28" s="1">
-        <v>55.81</v>
+        <v>74.42</v>
       </c>
       <c r="H28" s="1">
-        <v>44.19</v>
+        <v>25.58</v>
       </c>
       <c r="I28" s="2">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J28">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>44.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2755,25 +2755,25 @@
         <v>29</v>
       </c>
       <c r="E29">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F29">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G29" s="1">
-        <v>62.07</v>
+        <v>75.86</v>
       </c>
       <c r="H29" s="1">
-        <v>37.93</v>
+        <v>24.14</v>
       </c>
       <c r="I29" s="2">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="J29">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>37.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2822,22 +2822,22 @@
         <v>52</v>
       </c>
       <c r="D31">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31">
         <v>23</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31" s="1">
-        <v>74.19</v>
+        <v>71.88</v>
       </c>
       <c r="H31" s="1">
-        <v>25.81</v>
+        <v>28.13</v>
       </c>
       <c r="I31" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -3017,25 +3017,25 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3052,25 +3052,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3087,25 +3087,25 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>76.19</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>23.81</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>23.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3122,25 +3122,25 @@
         <v>22</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>68.18000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="H5" s="1">
-        <v>31.82</v>
+        <v>22.73</v>
       </c>
       <c r="I5" s="2">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3157,25 +3157,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>83.87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>16.13</v>
+        <v>12.9</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3192,25 +3192,25 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
-        <v>52.63</v>
+        <v>55.26</v>
       </c>
       <c r="H7" s="1">
-        <v>47.37</v>
+        <v>44.74</v>
       </c>
       <c r="I7" s="2">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3227,25 +3227,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>77.14</v>
+        <v>80</v>
       </c>
       <c r="H8" s="1">
-        <v>22.86</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3262,25 +3262,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="H9" s="1">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="I9" s="2">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>21.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3297,19 +3297,19 @@
         <v>36</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>86.11</v>
+        <v>75</v>
       </c>
       <c r="H10" s="1">
-        <v>13.89</v>
+        <v>25</v>
       </c>
       <c r="I10" s="2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3332,25 +3332,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>72.09</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>27.91</v>
+        <v>23.26</v>
       </c>
       <c r="I11" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3367,19 +3367,19 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1">
-        <v>88.37</v>
+        <v>74.42</v>
       </c>
       <c r="H12" s="1">
-        <v>11.63</v>
+        <v>25.58</v>
       </c>
       <c r="I12" s="2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>8.33</v>
       </c>
       <c r="I13" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         <v>19.35</v>
       </c>
       <c r="I14" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3472,16 +3472,16 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>66.67</v>
+        <v>76.19</v>
       </c>
       <c r="H15" s="1">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
       <c r="I15" s="2">
         <v>7.1</v>
@@ -3519,7 +3519,7 @@
         <v>5.71</v>
       </c>
       <c r="I16" s="2">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3542,16 +3542,16 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>80.95</v>
+        <v>76.19</v>
       </c>
       <c r="H17" s="1">
-        <v>19.05</v>
+        <v>23.81</v>
       </c>
       <c r="I17" s="2">
         <v>7</v>
@@ -3577,19 +3577,19 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F18">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>73.68000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>26.32</v>
+        <v>5.26</v>
       </c>
       <c r="I18" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3612,19 +3612,19 @@
         <v>35</v>
       </c>
       <c r="E19">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3647,19 +3647,19 @@
         <v>26</v>
       </c>
       <c r="E20">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>73.08</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>26.92</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>4.35</v>
       </c>
       <c r="I21" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3717,19 +3717,19 @@
         <v>32</v>
       </c>
       <c r="E22">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>31.25</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3764,7 +3764,7 @@
         <v>2.94</v>
       </c>
       <c r="I23" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3787,19 +3787,19 @@
         <v>36</v>
       </c>
       <c r="E24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G24" s="1">
-        <v>58.33</v>
+        <v>61.11</v>
       </c>
       <c r="H24" s="1">
-        <v>41.67</v>
+        <v>38.89</v>
       </c>
       <c r="I24" s="2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3822,19 +3822,19 @@
         <v>39</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="1">
-        <v>74.36</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>25.64</v>
+        <v>28.21</v>
       </c>
       <c r="I25" s="2">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3857,19 +3857,19 @@
         <v>36</v>
       </c>
       <c r="E26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F26">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G26" s="1">
-        <v>66.67</v>
+        <v>69.44</v>
       </c>
       <c r="H26" s="1">
-        <v>33.33</v>
+        <v>30.56</v>
       </c>
       <c r="I26" s="2">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3892,19 +3892,19 @@
         <v>32</v>
       </c>
       <c r="E27">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>68.75</v>
+        <v>87.5</v>
       </c>
       <c r="H27" s="1">
-        <v>31.25</v>
+        <v>12.5</v>
       </c>
       <c r="I27" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3927,19 +3927,19 @@
         <v>43</v>
       </c>
       <c r="E28">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" s="1">
-        <v>83.72</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H28" s="1">
-        <v>16.28</v>
+        <v>18.6</v>
       </c>
       <c r="I28" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3962,19 +3962,19 @@
         <v>29</v>
       </c>
       <c r="E29">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1">
-        <v>79.31</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H29" s="1">
-        <v>20.69</v>
+        <v>13.79</v>
       </c>
       <c r="I29" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3997,19 +3997,19 @@
         <v>34</v>
       </c>
       <c r="E30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1">
-        <v>82.34999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H30" s="1">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
       <c r="I30" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4029,22 +4029,22 @@
         <v>52</v>
       </c>
       <c r="D31">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G31" s="1">
-        <v>74.19</v>
+        <v>81.25</v>
       </c>
       <c r="H31" s="1">
-        <v>25.81</v>
+        <v>18.75</v>
       </c>
       <c r="I31" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4067,16 +4067,16 @@
         <v>25</v>
       </c>
       <c r="E32">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F32">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G32" s="1">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="H32" s="1">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I32" s="2">
         <v>7.2</v>
@@ -4102,16 +4102,16 @@
         <v>35</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G33" s="1">
-        <v>71.43000000000001</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H33" s="1">
-        <v>28.57</v>
+        <v>25.71</v>
       </c>
       <c r="I33" s="2">
         <v>7.3</v>
@@ -4137,19 +4137,19 @@
         <v>33</v>
       </c>
       <c r="E34">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F34">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G34" s="1">
-        <v>57.58</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>42.42</v>
+        <v>18.18</v>
       </c>
       <c r="I34" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J34">
         <v>0</v>
